--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260917_223054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260917_223054.xlsx
@@ -6406,7 +6406,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260917_223054.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260917_223054.xlsx
@@ -6406,7 +6406,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
